--- a/academias/Electricidad - Estadisticos 20231.xlsx
+++ b/academias/Electricidad - Estadisticos 20231.xlsx
@@ -560,25 +560,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -627,25 +627,25 @@
         <v>90</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="I5" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -936,25 +936,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1003,25 +1003,25 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1108,25 +1108,25 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="I19" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1175,25 +1175,25 @@
         <v>108</v>
       </c>
       <c r="E21">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>90.7</v>
+        <v>91.7</v>
       </c>
       <c r="H21" s="1">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="2">
         <v>7.9</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1204,25 +1204,25 @@
         <v>432</v>
       </c>
       <c r="E22">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="F22">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
-        <v>86.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="H22" s="1">
-        <v>13.4</v>
+        <v>6</v>
       </c>
       <c r="I22" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1290,25 +1290,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>90</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F5">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>3.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>90</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F9">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1564,25 +1564,25 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>21.4</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1599,25 +1599,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1634,25 +1634,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1666,25 +1666,25 @@
         <v>84</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F13">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1701,25 +1701,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1736,25 +1736,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1768,25 +1768,25 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>1.7</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1803,25 +1803,25 @@
         <v>25</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1838,25 +1838,25 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1873,25 +1873,25 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1908,25 +1908,25 @@
         <v>28</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J20">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1940,25 +1940,25 @@
         <v>108</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F21">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>2.8</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1969,25 +1969,25 @@
         <v>432</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="F22">
-        <v>432</v>
+        <v>25</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>94.2</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>5.8</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2090,25 +2090,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>96.7</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2">
         <v>8.1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2137,7 +2137,7 @@
         <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2157,25 +2157,25 @@
         <v>90</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>97.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2192,19 +2192,19 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2227,19 +2227,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>90</v>
+        <v>96.7</v>
       </c>
       <c r="H7" s="1">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2262,16 +2262,16 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>96.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H8" s="1">
-        <v>3.6</v>
+        <v>10.7</v>
       </c>
       <c r="I8" s="2">
         <v>8.5</v>
@@ -2294,16 +2294,16 @@
         <v>90</v>
       </c>
       <c r="E9">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>95.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="I9" s="2">
         <v>8.6</v>
@@ -2341,7 +2341,7 @@
         <v>21.4</v>
       </c>
       <c r="I10" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="H11" s="1">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="I11" s="2">
         <v>7.5</v>
@@ -2399,19 +2399,19 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>92.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H12" s="1">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>14.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2466,25 +2466,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2501,19 +2501,19 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I15" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2533,25 +2533,25 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>50</v>
+        <v>98.3</v>
       </c>
       <c r="H16" s="1">
-        <v>50</v>
+        <v>1.7</v>
       </c>
       <c r="I16" s="2">
-        <v>4.3</v>
+        <v>8.9</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2580,7 +2580,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2603,19 +2603,19 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H18" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2638,25 +2638,25 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>8.6</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2673,19 +2673,19 @@
         <v>28</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2705,25 +2705,25 @@
         <v>108</v>
       </c>
       <c r="E21">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>90.7</v>
+        <v>97.2</v>
       </c>
       <c r="H21" s="1">
-        <v>9.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I21" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2734,25 +2734,25 @@
         <v>432</v>
       </c>
       <c r="E22">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="F22">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G22" s="1">
-        <v>86.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="H22" s="1">
-        <v>13.4</v>
+        <v>5.8</v>
       </c>
       <c r="I22" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Electricidad - Estadisticos 20231.xlsx
+++ b/academias/Electricidad - Estadisticos 20231.xlsx
@@ -2055,19 +2055,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2157,16 +2157,16 @@
         <v>90</v>
       </c>
       <c r="E5">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="H5" s="1">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I5" s="2">
         <v>8.199999999999999</v>
@@ -2204,7 +2204,7 @@
         <v>3.1</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2227,19 +2227,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>10.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>90</v>
       </c>
       <c r="E9">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>94.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2501,19 +2501,19 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2533,19 +2533,19 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2568,19 +2568,19 @@
         <v>25</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2603,19 +2603,19 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2673,19 +2673,19 @@
         <v>28</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2705,16 +2705,16 @@
         <v>108</v>
       </c>
       <c r="E21">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
         <v>8.199999999999999</v>
@@ -2734,19 +2734,19 @@
         <v>432</v>
       </c>
       <c r="E22">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F22">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G22" s="1">
-        <v>94.2</v>
+        <v>95.8</v>
       </c>
       <c r="H22" s="1">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="I22" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20231.xlsx
+++ b/academias/Electricidad - Estadisticos 20231.xlsx
@@ -2329,19 +2329,19 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>78.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H10" s="1">
-        <v>21.4</v>
+        <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2364,19 +2364,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2399,19 +2399,19 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2431,19 +2431,19 @@
         <v>84</v>
       </c>
       <c r="E13">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="H13" s="1">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2734,19 +2734,19 @@
         <v>432</v>
       </c>
       <c r="E22">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1">
-        <v>95.8</v>
+        <v>96.8</v>
       </c>
       <c r="H22" s="1">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20231.xlsx
+++ b/academias/Electricidad - Estadisticos 20231.xlsx
@@ -2067,7 +2067,7 @@
         <v>3.1</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>2.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>3.1</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>10.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2306,7 +2306,7 @@
         <v>4.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>9.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>3.2</v>
       </c>
       <c r="I22" s="2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20231.xlsx
+++ b/academias/Electricidad - Estadisticos 20231.xlsx
@@ -2067,7 +2067,7 @@
         <v>3.1</v>
       </c>
       <c r="I2" s="2">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>2.2</v>
       </c>
       <c r="I5" s="2">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>3.1</v>
       </c>
       <c r="I6" s="2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>10.7</v>
       </c>
       <c r="I8" s="2">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2306,7 +2306,7 @@
         <v>4.4</v>
       </c>
       <c r="I9" s="2">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="2">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>9.5</v>
       </c>
       <c r="I13" s="2">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>3.2</v>
       </c>
       <c r="I22" s="2">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
         <v>0</v>
